--- a/artfynd/A 11982-2024 artfynd.xlsx
+++ b/artfynd/A 11982-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>80740618</v>
       </c>
       <c r="B2" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549171.1632958407</v>
+        <v>549171</v>
       </c>
       <c r="R2" t="n">
-        <v>6974848.826887175</v>
+        <v>6974849</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-10-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80740622</v>
+        <v>80740619</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549159.7910849127</v>
+        <v>549174</v>
       </c>
       <c r="R3" t="n">
-        <v>6974845.919953065</v>
+        <v>6974846</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-10-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80740632</v>
+        <v>81787088</v>
       </c>
       <c r="B4" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549158.0540251649</v>
+        <v>549149</v>
       </c>
       <c r="R4" t="n">
-        <v>6974839.965857214</v>
+        <v>6974771</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,19 +937,9 @@
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-10-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80740619</v>
+        <v>81787089</v>
       </c>
       <c r="B5" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549173.9436175544</v>
+        <v>549145</v>
       </c>
       <c r="R5" t="n">
-        <v>6974846.132694658</v>
+        <v>6974818</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,19 +1034,9 @@
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-10-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>80740620</v>
+        <v>81787125</v>
       </c>
       <c r="B6" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549181.1933098697</v>
+        <v>549223</v>
       </c>
       <c r="R6" t="n">
-        <v>6974849.889684219</v>
+        <v>6974624</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,19 +1131,9 @@
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-10-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,27 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>80740617</v>
+        <v>81787127</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549192.9357485515</v>
+        <v>549216</v>
       </c>
       <c r="R7" t="n">
-        <v>6974828.17827907</v>
+        <v>6974698</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,19 +1228,9 @@
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-10-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,49 +1245,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>81787094</v>
+        <v>80740620</v>
       </c>
       <c r="B8" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549178.0524172263</v>
+        <v>549181</v>
       </c>
       <c r="R8" t="n">
-        <v>6974846.194469817</v>
+        <v>6974850</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,21 +1325,11 @@
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1443,36 +1338,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Grov granlåga</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>81787127</v>
+        <v>80740621</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549215.8982693222</v>
+        <v>549129</v>
       </c>
       <c r="R9" t="n">
-        <v>6974698.104724916</v>
+        <v>6974845</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1537,19 +1422,9 @@
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2019-10-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,69 +1439,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>81787083</v>
+        <v>80740630</v>
       </c>
       <c r="B10" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storåsen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549275.037013805</v>
+        <v>549154</v>
       </c>
       <c r="R10" t="n">
-        <v>6974773.781445614</v>
+        <v>6974833</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1653,19 +1519,9 @@
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2019-10-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1680,12 +1536,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1695,12 +1551,7 @@
         <v>81787090</v>
       </c>
       <c r="B11" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1732,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549163.1649835603</v>
+        <v>549163</v>
       </c>
       <c r="R11" t="n">
-        <v>6974834.11467606</v>
+        <v>6974834</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1765,19 +1616,9 @@
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2019-10-14</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>81787119</v>
+        <v>81787094</v>
       </c>
       <c r="B12" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549215.1261682243</v>
+        <v>549178</v>
       </c>
       <c r="R12" t="n">
-        <v>6974719.069938274</v>
+        <v>6974846</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1877,21 +1713,11 @@
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1900,6 +1726,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Grov granlåga</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1916,15 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>81787128</v>
+        <v>81787119</v>
       </c>
       <c r="B13" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>549219.0392652611</v>
+        <v>549215</v>
       </c>
       <c r="R13" t="n">
-        <v>6974701.80014056</v>
+        <v>6974719</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1989,21 +1815,11 @@
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2012,14 +1828,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Asp</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2036,37 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>81787091</v>
+        <v>80740631</v>
       </c>
       <c r="B14" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2076,13 +1879,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>549188.8749188804</v>
+        <v>549153</v>
       </c>
       <c r="R14" t="n">
-        <v>6974824.92519626</v>
+        <v>6974822</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2109,21 +1912,11 @@
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2132,61 +1925,48 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Grov asp</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>81787120</v>
+        <v>81787128</v>
       </c>
       <c r="B15" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2196,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>549184.9252418427</v>
+        <v>549219</v>
       </c>
       <c r="R15" t="n">
-        <v>6974723.175834535</v>
+        <v>6974702</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2229,21 +2009,11 @@
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2253,9 +2023,12 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AN15" t="n">
+        <v>1</v>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>1 substratenheter # Asp</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2273,37 +2046,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>81787092</v>
+        <v>80740617</v>
       </c>
       <c r="B16" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2313,13 +2081,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>549188.8749188804</v>
+        <v>549193</v>
       </c>
       <c r="R16" t="n">
-        <v>6974824.92519626</v>
+        <v>6974828</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2346,21 +2114,11 @@
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2369,39 +2127,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Grov asp</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>81787085</v>
+        <v>80740622</v>
       </c>
       <c r="B17" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2433,13 +2178,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549302.8694230468</v>
+        <v>549160</v>
       </c>
       <c r="R17" t="n">
-        <v>6974745.016122718</v>
+        <v>6974846</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2466,21 +2211,11 @@
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2489,36 +2224,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Björk</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>81787130</v>
+        <v>80740633</v>
       </c>
       <c r="B18" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2550,13 +2275,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549214.8959856696</v>
+        <v>549151</v>
       </c>
       <c r="R18" t="n">
-        <v>6974704.0178928</v>
+        <v>6974844</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2583,21 +2308,11 @@
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2606,39 +2321,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Björkhögstubbe</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>81787129</v>
+        <v>81787085</v>
       </c>
       <c r="B19" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2670,10 +2372,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549219.0392652611</v>
+        <v>549303</v>
       </c>
       <c r="R19" t="n">
-        <v>6974701.80014056</v>
+        <v>6974745</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2703,21 +2405,11 @@
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2727,12 +2419,9 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AN19" t="n">
-        <v>1</v>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>1 substratenheter # Asp</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2750,15 +2439,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>81787126</v>
+        <v>81787086</v>
       </c>
       <c r="B20" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2790,13 +2474,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549223.7969047353</v>
+        <v>549326</v>
       </c>
       <c r="R20" t="n">
-        <v>6974689.103175421</v>
+        <v>6974740</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2823,21 +2507,11 @@
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2847,12 +2521,9 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AN20" t="n">
-        <v>6</v>
-      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>6 substratenheter # Klen asp och sälg</t>
+          <t>Asplåga</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2873,12 +2544,7 @@
         <v>81787093</v>
       </c>
       <c r="B21" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2910,10 +2576,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549188.8749188804</v>
+        <v>549189</v>
       </c>
       <c r="R21" t="n">
-        <v>6974824.92519626</v>
+        <v>6974825</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2943,19 +2609,9 @@
           <t>2019-10-14</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2019-10-14</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2987,6 +2643,1142 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>81787120</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>549185</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6974723</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2019-10-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2019-10-14</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>81787124</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>549228</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6974625</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2019-10-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2019-10-14</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>2 substratenheter # Asp</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>81787126</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>549224</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6974689</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2019-10-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2019-10-14</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>6 substratenheter # Klen asp och sälg</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>81787129</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>549219</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6974702</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2019-10-14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2019-10-14</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Asp</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>81787130</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>549215</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6974704</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2019-10-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2019-10-14</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Björkhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>80740632</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>549158</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6974840</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2019-10-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2019-10-14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>81787092</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>549189</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6974825</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2019-10-14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2019-10-14</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Grov asp</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>81787123</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>549228</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6974625</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2019-10-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2019-10-14</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>2 substratenheter # Asp</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>81787091</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>549189</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6974825</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2019-10-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2019-10-14</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Grov asp</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>81787083</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>549275</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6974774</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2019-10-14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2019-10-14</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>81787121</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>549155</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6974763</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2019-10-14</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2019-10-14</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11982-2024 artfynd.xlsx
+++ b/artfynd/A 11982-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80740618</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80740619</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81787088</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81787089</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81787125</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81787127</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80740620</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80740621</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80740630</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81787090</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81787094</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81787119</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1938,6 +2003,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80740631</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2043,6 +2113,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81787128</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2140,6 +2215,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80740617</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2237,6 +2317,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80740622</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2334,6 +2419,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80740633</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2436,6 +2526,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81787085</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2538,6 +2633,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81787086</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2643,6 +2743,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81787093</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2745,6 +2850,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81787120</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2850,6 +2960,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81787124</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2955,6 +3070,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81787126</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3060,6 +3180,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81787129</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3165,6 +3290,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81787130</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3262,6 +3392,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80740632</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3367,6 +3502,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81787092</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3472,6 +3612,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81787123</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3577,6 +3722,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81787091</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3678,6 +3828,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81787083</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3779,8 +3934,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81787121</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>